--- a/keywords.xlsx
+++ b/keywords.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gilgi\Desktop\이하은-주문장\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{670DCA39-7068-4FD8-81EE-BE1F2A473DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DABDC67-FEF1-4B5D-AAC4-A473129C6127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="132">
   <si>
     <t>키워드</t>
   </si>
@@ -399,6 +399,110 @@
   </si>
   <si>
     <t>(1호(1-2세)~6호(11-12세))</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S-JXL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(JM)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(~5X)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(XL~XXL)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(J1~J2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2XL~)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(XL~JS)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> (겨울 세일)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1(S~M)~2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> S-JS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(S~JS)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(L~JS(2X))</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>17-19</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(2XL~J2)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(12m~120)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(S(0)~XL(3))</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S-JS</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(11~15)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(XS~L)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(S~M)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1P)(BABY~4)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>XS-JL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(1(S~M)~3(XL~J1))</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(5호~11호)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(XS~M)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>(80~90)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -439,7 +543,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -816,7 +920,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A113"/>
+  <dimension ref="A1:A144"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -1234,8 +1338,8 @@
         <v>79</v>
       </c>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+    <row r="84" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1382,6 +1486,161 @@
     <row r="113" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
